--- a/Result/profitability/1808.xlsx
+++ b/Result/profitability/1808.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3887500000000003</v>
+        <v>0.5150000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>29.78</v>
+        <v>28.08125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3912500000000002</v>
+        <v>0.6050000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>29.6575</v>
+        <v>29.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5000000000000002</v>
+        <v>0.7012500000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>30.465</v>
+        <v>28.7275</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6162500000000003</v>
+        <v>0.8087500000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>30.48</v>
+        <v>31.6175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6800000000000003</v>
+        <v>0.8800000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>32.395</v>
+        <v>35.36499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8062500000000002</v>
+        <v>0.7712500000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>35.39375</v>
+        <v>33.71875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6462500000000002</v>
+        <v>0.6962500000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>35.90375</v>
+        <v>35.69375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7068</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5254</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>71</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1591</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5112500000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.28125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3773584905660377</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0614259597806216</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-19.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5491852745926373</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
